--- a/09-运维服务人员管理相关制度/word/09-07年度招聘计划.xlsx
+++ b/09-运维服务人员管理相关制度/word/09-07年度招聘计划.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19935" windowHeight="7935"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="19935" windowHeight="7935" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
-    <t>青岛九邮信息技术有限公司2019年招聘计划</t>
+    <t>南京航之舟数字科技有限公司2025年招聘计划</t>
   </si>
   <si>
     <t>部门</t>
@@ -60,6 +61,12 @@
 3、具有独立处理系统故障的能力。
 </t>
   </si>
+  <si>
+    <t>2025.6</t>
+  </si>
+  <si>
+    <t>2025.9</t>
+  </si>
 </sst>
 </file>
 
@@ -71,17 +78,24 @@
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -89,6 +103,7 @@
       <sz val="20"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -96,19 +111,22 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -116,26 +134,24 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -143,28 +159,24 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -172,7 +184,8 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -180,7 +193,8 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -188,6 +202,7 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -196,29 +211,33 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -226,14 +245,16 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -241,6 +262,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -249,208 +271,210 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -461,60 +485,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -530,36 +500,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -574,253 +514,457 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.49998"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="55">
+  <cellStyleXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="6" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="51" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="55">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="Currency" xfId="12"/>
-    <cellStyle name="已访问的超链接" xfId="13" builtinId="9"/>
-    <cellStyle name="注释" xfId="14" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="15" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="16" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="17" builtinId="11"/>
-    <cellStyle name="标题" xfId="18" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="19" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="20" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="21" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="22" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="23" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="24" builtinId="44"/>
-    <cellStyle name="输出" xfId="25" builtinId="21"/>
-    <cellStyle name="计算" xfId="26" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="27" builtinId="23"/>
-    <cellStyle name="Currency [0]" xfId="28"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="29" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="30" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="31" builtinId="24"/>
-    <cellStyle name="汇总" xfId="32" builtinId="25"/>
-    <cellStyle name="好" xfId="33" builtinId="26"/>
-    <cellStyle name="适中" xfId="34" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="35" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="36" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="37" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="38" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="39" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="40" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="41" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="42" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="43" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="44" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="45" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="46" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="47" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="48" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="49" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="50" builtinId="52"/>
-    <cellStyle name="Normal" xfId="51"/>
-    <cellStyle name="Percent" xfId="52"/>
-    <cellStyle name="Comma" xfId="53"/>
-    <cellStyle name="Comma [0]" xfId="54"/>
+  <cellStyles count="79">
+    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Percent" xfId="15"/>
+    <cellStyle name="Currency" xfId="16"/>
+    <cellStyle name="Currency [0]" xfId="17"/>
+    <cellStyle name="Comma" xfId="18"/>
+    <cellStyle name="Comma [0]" xfId="19"/>
+    <cellStyle name="Percent" xfId="20"/>
+    <cellStyle name="Currency" xfId="21"/>
+    <cellStyle name="Currency [0]" xfId="22"/>
+    <cellStyle name="Comma" xfId="23"/>
+    <cellStyle name="Comma [0]" xfId="24"/>
+    <cellStyle name="Percent" xfId="25"/>
+    <cellStyle name="Currency" xfId="26"/>
+    <cellStyle name="Currency [0]" xfId="27"/>
+    <cellStyle name="Comma" xfId="28"/>
+    <cellStyle name="Comma [0]" xfId="29"/>
+    <cellStyle name="Percent" xfId="30"/>
+    <cellStyle name="Currency" xfId="31"/>
+    <cellStyle name="Currency [0]" xfId="32"/>
+    <cellStyle name="Comma" xfId="33"/>
+    <cellStyle name="Comma [0]" xfId="34"/>
+    <cellStyle name="Percent" xfId="35"/>
+    <cellStyle name="Currency" xfId="36"/>
+    <cellStyle name="Currency [0]" xfId="37"/>
+    <cellStyle name="Comma" xfId="38"/>
+    <cellStyle name="Comma [0]" xfId="39"/>
+    <cellStyle name="货币[0]" xfId="40"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="41"/>
+    <cellStyle name="输入" xfId="42"/>
+    <cellStyle name="货币" xfId="43"/>
+    <cellStyle name="千位分隔[0]" xfId="44"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="45"/>
+    <cellStyle name="差" xfId="46"/>
+    <cellStyle name="千位分隔" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="48"/>
+    <cellStyle name="超链接" xfId="49"/>
+    <cellStyle name="百分比" xfId="50"/>
+    <cellStyle name="Currency" xfId="51"/>
+    <cellStyle name="已访问的超链接" xfId="52"/>
+    <cellStyle name="注释" xfId="53"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="54"/>
+    <cellStyle name="标题 4" xfId="55"/>
+    <cellStyle name="警告文本" xfId="56"/>
+    <cellStyle name="标题" xfId="57"/>
+    <cellStyle name="解释性文本" xfId="58"/>
+    <cellStyle name="标题 1" xfId="59"/>
+    <cellStyle name="标题 2" xfId="60"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="61"/>
+    <cellStyle name="标题 3" xfId="62"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="63"/>
+    <cellStyle name="输出" xfId="64"/>
+    <cellStyle name="计算" xfId="65"/>
+    <cellStyle name="检查单元格" xfId="66"/>
+    <cellStyle name="Currency [0]" xfId="67"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="68"/>
+    <cellStyle name="强调文字颜色 2" xfId="69"/>
+    <cellStyle name="链接单元格" xfId="70"/>
+    <cellStyle name="汇总" xfId="71"/>
+    <cellStyle name="好" xfId="72"/>
+    <cellStyle name="适中" xfId="73"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="74"/>
+    <cellStyle name="强调文字颜色 1" xfId="75"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="76"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="77"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="78"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="79"/>
+    <cellStyle name="强调文字颜色 3" xfId="80"/>
+    <cellStyle name="强调文字颜色 4" xfId="81"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="82"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="83"/>
+    <cellStyle name="强调文字颜色 5" xfId="84"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="85"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="86"/>
+    <cellStyle name="强调文字颜色 6" xfId="87"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="88"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="89"/>
+    <cellStyle name="Percent" xfId="90"/>
+    <cellStyle name="Comma" xfId="91"/>
+    <cellStyle name="Comma [0]" xfId="92"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1163,16 +1307,16 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelRow="4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.6333333333333" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="7" style="2" customWidth="1"/>
-    <col min="4" max="4" width="49.3833333333333" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.1333333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.6333333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="49.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.625" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" spans="1:6">
+    <row r="1" spans="1:6" ht="13.5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1182,7 +1326,7 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" ht="13.5" spans="1:6">
+    <row r="2" spans="1:6" ht="13.5">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1190,7 +1334,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="37.5" customHeight="1" spans="1:8">
+    <row r="3" spans="1:8" s="1" customFormat="1" ht="37.5" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1211,7 +1355,7 @@
       </c>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" ht="57" spans="1:6">
+    <row r="4" spans="1:6" ht="57">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -1227,11 +1371,11 @@
       <c r="E4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="5">
-        <v>2019.6</v>
+      <c r="F4" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5" ht="114.75" customHeight="1" spans="1:6">
+    <row r="5" spans="1:6" ht="114.75" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -1247,8 +1391,8 @@
       <c r="E5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="6">
-        <v>2019.9</v>
+      <c r="F5" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1257,7 +1401,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.118055555555556" right="0.118055555555556" top="0.156944444444444" bottom="0.156944444444444" header="0.314583333333333" footer="0.314583333333333"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+  <pageSetup fitToHeight="0" orientation="landscape" paperSize="9"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>